--- a/Reports/Mohid Logs.xlsx
+++ b/Reports/Mohid Logs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mirzam\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohid\OneDrive\Documents\GitHub\Concept-Mapping-Concept-Extraction\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{112E1C5F-F397-4567-A24D-621375FBF091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F69E49-C4C5-4593-AC5B-6E81A84A5E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D0D780D9-74C2-490A-AAE6-A52FB895CA23}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{D0D780D9-74C2-490A-AAE6-A52FB895CA23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>30 mins</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
   <si>
     <t>Researching on different computer vision models that could be implemented</t>
   </si>
@@ -48,7 +45,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,18 +411,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB32EA3-4582-4232-838D-0AAA6B408025}">
-  <dimension ref="A2:C2"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A2:J10"/>
+  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <cols>
+    <col min="1" max="1" width="8.953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1">
-        <v>46042</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.75">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.75">
+      <c r="J10" t="s">
         <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Mohid Logs.xlsx
+++ b/Reports/Mohid Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohid\OneDrive\Documents\GitHub\Concept-Mapping-Concept-Extraction\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38F69E49-C4C5-4593-AC5B-6E81A84A5E6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6832A7E0-C4CE-4AB2-81D4-59BEAAADD8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{D0D780D9-74C2-490A-AAE6-A52FB895CA23}"/>
+    <workbookView xWindow="9525" yWindow="0" windowWidth="9750" windowHeight="11355" xr2:uid="{D0D780D9-74C2-490A-AAE6-A52FB895CA23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,75 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Researching on different computer vision models that could be implemented</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Task Description</t>
+  </si>
+  <si>
+    <t>Time spent (hours)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Met with partner </t>
+  </si>
+  <si>
+    <t>Project Research</t>
+  </si>
+  <si>
+    <t>Powerpoint extraction</t>
+  </si>
+  <si>
+    <t>Getting all extractions</t>
+  </si>
+  <si>
+    <t>Create the visuals</t>
+  </si>
+  <si>
+    <t>Worked on Design objectives</t>
+  </si>
+  <si>
+    <t>Proofread objectives</t>
+  </si>
+  <si>
+    <t>Added image description</t>
+  </si>
+  <si>
+    <t>Waited for access</t>
+  </si>
+  <si>
+    <t>Built training set</t>
+  </si>
+  <si>
+    <t>2/29/2026</t>
+  </si>
+  <si>
+    <t>Tested training set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tested first model </t>
+  </si>
+  <si>
+    <t>Tested new model</t>
+  </si>
+  <si>
+    <t>Worked on Midterm Report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finalized Report </t>
+  </si>
+  <si>
+    <t>Worked on PDF Extractor</t>
+  </si>
+  <si>
+    <t>Started Training TinyLlama Model</t>
+  </si>
+  <si>
+    <t>Created a way to extract Alt Text</t>
+  </si>
+  <si>
+    <t>Setup The GPU Pass Through</t>
   </si>
 </sst>
 </file>
@@ -74,9 +140,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -411,18 +485,258 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEB32EA3-4582-4232-838D-0AAA6B408025}">
-  <dimension ref="A2:J10"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
-    <col min="1" max="1" width="8.953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="27.04296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.2265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.75">
-      <c r="A2" s="1"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.75">
-      <c r="J10" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A1" t="s">
         <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A2" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A3" s="1">
+        <v>46040</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="2">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <f>SUM(C2:C38)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A4" s="1">
+        <v>45676</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A5" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A6" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A7" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A8" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A9" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A10" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A11" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A12" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A13" s="1">
+        <v>46073</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A14" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B14" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A15" s="1">
+        <v>46081</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="A16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A17" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A18" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A19" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A20" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A21" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.75">
+      <c r="A22" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="2">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Reports/Mohid Logs.xlsx
+++ b/Reports/Mohid Logs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mohid\OneDrive\Documents\GitHub\Concept-Mapping-Concept-Extraction\Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6832A7E0-C4CE-4AB2-81D4-59BEAAADD8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E0780A-6F0E-4D2F-A083-6AFD1DE63A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9525" yWindow="0" windowWidth="9750" windowHeight="11355" xr2:uid="{D0D780D9-74C2-490A-AAE6-A52FB895CA23}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{D0D780D9-74C2-490A-AAE6-A52FB895CA23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="24">
   <si>
     <t>Date</t>
   </si>
@@ -105,6 +105,9 @@
   </si>
   <si>
     <t>Setup The GPU Pass Through</t>
+  </si>
+  <si>
+    <t>Total Worked (hours)</t>
   </si>
 </sst>
 </file>
@@ -491,6 +494,7 @@
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="27.04296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.2265625" customWidth="1"/>
+    <col min="5" max="5" width="17.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.75">
@@ -503,6 +507,9 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="E1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A2" s="1">
@@ -514,6 +521,10 @@
       <c r="C2" s="2">
         <v>1</v>
       </c>
+      <c r="E2">
+        <f>SUM(C2:C38)</f>
+        <v>53</v>
+      </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A3" s="1">
@@ -525,10 +536,6 @@
       <c r="C3" s="2">
         <v>5</v>
       </c>
-      <c r="E3">
-        <f>SUM(C2:C38)</f>
-        <v>55</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.75">
       <c r="A4" s="1">
@@ -714,7 +721,7 @@
         <v>17</v>
       </c>
       <c r="C20" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.75">
